--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3078,7 +3079,7 @@
         </is>
       </c>
       <c r="B52" s="0" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>46234.7</v>
@@ -3090,7 +3091,7 @@
         <v>39384.85</v>
       </c>
       <c r="F52" s="0" t="n">
-        <v>39933.3</v>
+        <v>43119.75</v>
       </c>
       <c r="G52" s="0" t="n">
         <v>48218.87</v>
@@ -3122,7 +3123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N625"/>
+  <dimension ref="A1:N626"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26380,6 +26381,41 @@
         <v/>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="62" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B626" t="n">
+        <v>41610.41</v>
+      </c>
+      <c r="C626" t="n">
+        <v>43214.36</v>
+      </c>
+      <c r="D626" t="n">
+        <v>41610.41</v>
+      </c>
+      <c r="E626" t="n">
+        <v>43119.75</v>
+      </c>
+      <c r="F626" t="n">
+        <v>3186.45</v>
+      </c>
+      <c r="G626" t="n">
+        <v>43723.63</v>
+      </c>
+      <c r="H626" s="55">
+        <f>E626-G626</f>
+        <v/>
+      </c>
+      <c r="I626" s="34">
+        <f>H626/1000</f>
+        <v/>
+      </c>
+      <c r="J626" s="34">
+        <f>AVERAGE(I625:I626)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="6.5" defaultRowHeight="16.5"/>
   <cols>
     <col width="5.875" customWidth="1" style="1" min="1" max="1"/>
@@ -3107,8 +3107,42 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>26M08</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>42780.42</v>
+      </c>
+      <c r="D53" t="n">
+        <v>43784.19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>42780.42</v>
+      </c>
+      <c r="F53" t="n">
+        <v>43386.41</v>
+      </c>
+      <c r="G53" t="n">
+        <v>47395.3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>39384.85</v>
+      </c>
+      <c r="I53" t="n">
+        <v>43390.075</v>
+      </c>
       <c r="J53" s="0" t="n">
         <v>43801.86</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" t="n">
+        <v>43390.075</v>
       </c>
     </row>
   </sheetData>
@@ -3123,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N626"/>
+  <dimension ref="A1:N627"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26385,22 +26419,22 @@
       <c r="A626" s="62" t="n">
         <v>46234</v>
       </c>
-      <c r="B626" t="n">
+      <c r="B626" s="0" t="n">
         <v>41610.41</v>
       </c>
-      <c r="C626" t="n">
+      <c r="C626" s="0" t="n">
         <v>43214.36</v>
       </c>
-      <c r="D626" t="n">
+      <c r="D626" s="0" t="n">
         <v>41610.41</v>
       </c>
-      <c r="E626" t="n">
+      <c r="E626" s="0" t="n">
         <v>43119.75</v>
       </c>
-      <c r="F626" t="n">
+      <c r="F626" s="0" t="n">
         <v>3186.45</v>
       </c>
-      <c r="G626" t="n">
+      <c r="G626" s="0" t="n">
         <v>43723.63</v>
       </c>
       <c r="H626" s="55">
@@ -26413,6 +26447,41 @@
       </c>
       <c r="J626" s="34">
         <f>AVERAGE(I625:I626)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="62" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B627" t="n">
+        <v>42780.42</v>
+      </c>
+      <c r="C627" t="n">
+        <v>43784.19</v>
+      </c>
+      <c r="D627" t="n">
+        <v>42780.42</v>
+      </c>
+      <c r="E627" t="n">
+        <v>43386.41</v>
+      </c>
+      <c r="F627" t="n">
+        <v>266.66</v>
+      </c>
+      <c r="G627" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H627" s="55">
+        <f>E627-G627</f>
+        <v/>
+      </c>
+      <c r="I627" s="34">
+        <f>H627/1000</f>
+        <v/>
+      </c>
+      <c r="J627" s="34">
+        <f>AVERAGE(I626:I627)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3107,33 +3107,33 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>26M08</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
+      <c r="B53" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
-      <c r="D53" t="n">
-        <v>43784.19</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" s="0" t="n">
+        <v>43912.77</v>
+      </c>
+      <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
-      <c r="F53" t="n">
-        <v>43386.41</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53" s="0" t="n">
+        <v>43360.66</v>
+      </c>
+      <c r="G53" s="0" t="n">
         <v>47395.3</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="0" t="n">
         <v>39384.85</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="J53" s="0" t="n">
@@ -3141,7 +3141,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="J54" t="n">
+      <c r="J54" s="0" t="n">
         <v>43390.075</v>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N627"/>
+  <dimension ref="A1:N628"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26454,22 +26454,22 @@
       <c r="A627" s="62" t="n">
         <v>46237</v>
       </c>
-      <c r="B627" t="n">
+      <c r="B627" s="0" t="n">
         <v>42780.42</v>
       </c>
-      <c r="C627" t="n">
+      <c r="C627" s="0" t="n">
         <v>43784.19</v>
       </c>
-      <c r="D627" t="n">
+      <c r="D627" s="0" t="n">
         <v>42780.42</v>
       </c>
-      <c r="E627" t="n">
+      <c r="E627" s="0" t="n">
         <v>43386.41</v>
       </c>
-      <c r="F627" t="n">
+      <c r="F627" s="0" t="n">
         <v>266.66</v>
       </c>
-      <c r="G627" t="n">
+      <c r="G627" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H627" s="55">
@@ -26482,6 +26482,41 @@
       </c>
       <c r="J627" s="34">
         <f>AVERAGE(I626:I627)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="62" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B628" t="n">
+        <v>43092.49</v>
+      </c>
+      <c r="C628" t="n">
+        <v>43912.77</v>
+      </c>
+      <c r="D628" t="n">
+        <v>42895.81</v>
+      </c>
+      <c r="E628" t="n">
+        <v>43360.66</v>
+      </c>
+      <c r="F628" t="n">
+        <v>-25.75</v>
+      </c>
+      <c r="G628" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H628" s="55">
+        <f>E628-G628</f>
+        <v/>
+      </c>
+      <c r="I628" s="34">
+        <f>H628/1000</f>
+        <v/>
+      </c>
+      <c r="J628" s="34">
+        <f>AVERAGE(I627:I628)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -26489,22 +26488,22 @@
       <c r="A628" s="62" t="n">
         <v>46238</v>
       </c>
-      <c r="B628" t="n">
+      <c r="B628" s="0" t="n">
         <v>43092.49</v>
       </c>
-      <c r="C628" t="n">
+      <c r="C628" s="0" t="n">
         <v>43912.77</v>
       </c>
-      <c r="D628" t="n">
+      <c r="D628" s="0" t="n">
         <v>42895.81</v>
       </c>
-      <c r="E628" t="n">
+      <c r="E628" s="0" t="n">
         <v>43360.66</v>
       </c>
-      <c r="F628" t="n">
+      <c r="F628" s="0" t="n">
         <v>-25.75</v>
       </c>
-      <c r="G628" t="n">
+      <c r="G628" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H628" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3112,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>43912.77</v>
+        <v>44980.31</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>43360.66</v>
+        <v>44611.6</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3156,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N628"/>
+  <dimension ref="A1:N629"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26519,6 +26520,41 @@
         <v/>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" s="62" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B629" t="n">
+        <v>43809.83</v>
+      </c>
+      <c r="C629" t="n">
+        <v>44980.31</v>
+      </c>
+      <c r="D629" t="n">
+        <v>43809.83</v>
+      </c>
+      <c r="E629" t="n">
+        <v>44611.6</v>
+      </c>
+      <c r="F629" t="n">
+        <v>1250.94</v>
+      </c>
+      <c r="G629" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H629" s="55">
+        <f>E629-G629</f>
+        <v/>
+      </c>
+      <c r="I629" s="34">
+        <f>H629/1000</f>
+        <v/>
+      </c>
+      <c r="J629" s="34">
+        <f>AVERAGE(I628:I629)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -26524,22 +26523,22 @@
       <c r="A629" s="62" t="n">
         <v>46239</v>
       </c>
-      <c r="B629" t="n">
+      <c r="B629" s="0" t="n">
         <v>43809.83</v>
       </c>
-      <c r="C629" t="n">
+      <c r="C629" s="0" t="n">
         <v>44980.31</v>
       </c>
-      <c r="D629" t="n">
+      <c r="D629" s="0" t="n">
         <v>43809.83</v>
       </c>
-      <c r="E629" t="n">
+      <c r="E629" s="0" t="n">
         <v>44611.6</v>
       </c>
-      <c r="F629" t="n">
+      <c r="F629" s="0" t="n">
         <v>1250.94</v>
       </c>
-      <c r="G629" t="n">
+      <c r="G629" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H629" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3112,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3124,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44611.6</v>
+        <v>44396.7</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3156,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N629"/>
+  <dimension ref="A1:N630"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26554,6 +26555,41 @@
         <v/>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="62" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B630" t="n">
+        <v>44487.94</v>
+      </c>
+      <c r="C630" t="n">
+        <v>44601.24</v>
+      </c>
+      <c r="D630" t="n">
+        <v>44024.32</v>
+      </c>
+      <c r="E630" t="n">
+        <v>44396.7</v>
+      </c>
+      <c r="F630" t="n">
+        <v>-214.9</v>
+      </c>
+      <c r="G630" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H630" s="55">
+        <f>E630-G630</f>
+        <v/>
+      </c>
+      <c r="I630" s="34">
+        <f>H630/1000</f>
+        <v/>
+      </c>
+      <c r="J630" s="34">
+        <f>AVERAGE(I629:I630)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44396.7</v>
+        <v>44225.91</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N630"/>
+  <dimension ref="A1:N631"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26559,22 +26559,22 @@
       <c r="A630" s="62" t="n">
         <v>46240</v>
       </c>
-      <c r="B630" t="n">
+      <c r="B630" s="0" t="n">
         <v>44487.94</v>
       </c>
-      <c r="C630" t="n">
+      <c r="C630" s="0" t="n">
         <v>44601.24</v>
       </c>
-      <c r="D630" t="n">
+      <c r="D630" s="0" t="n">
         <v>44024.32</v>
       </c>
-      <c r="E630" t="n">
+      <c r="E630" s="0" t="n">
         <v>44396.7</v>
       </c>
-      <c r="F630" t="n">
+      <c r="F630" s="0" t="n">
         <v>-214.9</v>
       </c>
-      <c r="G630" t="n">
+      <c r="G630" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H630" s="55">
@@ -26587,6 +26587,41 @@
       </c>
       <c r="J630" s="34">
         <f>AVERAGE(I629:I630)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="62" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B631" t="n">
+        <v>44450.19</v>
+      </c>
+      <c r="C631" t="n">
+        <v>44827.13</v>
+      </c>
+      <c r="D631" t="n">
+        <v>43941.56</v>
+      </c>
+      <c r="E631" t="n">
+        <v>44225.91</v>
+      </c>
+      <c r="F631" t="n">
+        <v>-170.79</v>
+      </c>
+      <c r="G631" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H631" s="55">
+        <f>E631-G631</f>
+        <v/>
+      </c>
+      <c r="I631" s="34">
+        <f>H631/1000</f>
+        <v/>
+      </c>
+      <c r="J631" s="34">
+        <f>AVERAGE(I630:I631)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>44980.31</v>
+        <v>45219.4</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44225.91</v>
+        <v>44928.76</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N631"/>
+  <dimension ref="A1:N632"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26594,22 +26594,22 @@
       <c r="A631" s="62" t="n">
         <v>46241</v>
       </c>
-      <c r="B631" t="n">
+      <c r="B631" s="0" t="n">
         <v>44450.19</v>
       </c>
-      <c r="C631" t="n">
+      <c r="C631" s="0" t="n">
         <v>44827.13</v>
       </c>
-      <c r="D631" t="n">
+      <c r="D631" s="0" t="n">
         <v>43941.56</v>
       </c>
-      <c r="E631" t="n">
+      <c r="E631" s="0" t="n">
         <v>44225.91</v>
       </c>
-      <c r="F631" t="n">
+      <c r="F631" s="0" t="n">
         <v>-170.79</v>
       </c>
-      <c r="G631" t="n">
+      <c r="G631" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H631" s="55">
@@ -26622,6 +26622,41 @@
       </c>
       <c r="J631" s="34">
         <f>AVERAGE(I630:I631)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="62" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B632" t="n">
+        <v>44540.71</v>
+      </c>
+      <c r="C632" t="n">
+        <v>45219.4</v>
+      </c>
+      <c r="D632" t="n">
+        <v>44540.71</v>
+      </c>
+      <c r="E632" t="n">
+        <v>44928.76</v>
+      </c>
+      <c r="F632" t="n">
+        <v>702.85</v>
+      </c>
+      <c r="G632" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H632" s="55">
+        <f>E632-G632</f>
+        <v/>
+      </c>
+      <c r="I632" s="34">
+        <f>H632/1000</f>
+        <v/>
+      </c>
+      <c r="J632" s="34">
+        <f>AVERAGE(I631:I632)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44928.76</v>
+        <v>45120.72</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N632"/>
+  <dimension ref="A1:N633"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26629,22 +26629,22 @@
       <c r="A632" s="62" t="n">
         <v>46244</v>
       </c>
-      <c r="B632" t="n">
+      <c r="B632" s="0" t="n">
         <v>44540.71</v>
       </c>
-      <c r="C632" t="n">
+      <c r="C632" s="0" t="n">
         <v>45219.4</v>
       </c>
-      <c r="D632" t="n">
+      <c r="D632" s="0" t="n">
         <v>44540.71</v>
       </c>
-      <c r="E632" t="n">
+      <c r="E632" s="0" t="n">
         <v>44928.76</v>
       </c>
-      <c r="F632" t="n">
+      <c r="F632" s="0" t="n">
         <v>702.85</v>
       </c>
-      <c r="G632" t="n">
+      <c r="G632" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H632" s="55">
@@ -26657,6 +26657,41 @@
       </c>
       <c r="J632" s="34">
         <f>AVERAGE(I631:I632)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="62" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B633" t="n">
+        <v>44883.9</v>
+      </c>
+      <c r="C633" t="n">
+        <v>45195.41</v>
+      </c>
+      <c r="D633" t="n">
+        <v>44652.06</v>
+      </c>
+      <c r="E633" t="n">
+        <v>45120.72</v>
+      </c>
+      <c r="F633" t="n">
+        <v>191.96</v>
+      </c>
+      <c r="G633" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H633" s="55">
+        <f>E633-G633</f>
+        <v/>
+      </c>
+      <c r="I633" s="34">
+        <f>H633/1000</f>
+        <v/>
+      </c>
+      <c r="J633" s="34">
+        <f>AVERAGE(I632:I633)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>45219.4</v>
+        <v>45529.48</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45120.72</v>
+        <v>45518.07</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N633"/>
+  <dimension ref="A1:N634"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26664,22 +26664,22 @@
       <c r="A633" s="62" t="n">
         <v>46245</v>
       </c>
-      <c r="B633" t="n">
+      <c r="B633" s="0" t="n">
         <v>44883.9</v>
       </c>
-      <c r="C633" t="n">
+      <c r="C633" s="0" t="n">
         <v>45195.41</v>
       </c>
-      <c r="D633" t="n">
+      <c r="D633" s="0" t="n">
         <v>44652.06</v>
       </c>
-      <c r="E633" t="n">
+      <c r="E633" s="0" t="n">
         <v>45120.72</v>
       </c>
-      <c r="F633" t="n">
+      <c r="F633" s="0" t="n">
         <v>191.96</v>
       </c>
-      <c r="G633" t="n">
+      <c r="G633" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H633" s="55">
@@ -26692,6 +26692,41 @@
       </c>
       <c r="J633" s="34">
         <f>AVERAGE(I632:I633)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="62" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B634" t="n">
+        <v>45175.7</v>
+      </c>
+      <c r="C634" t="n">
+        <v>45529.48</v>
+      </c>
+      <c r="D634" t="n">
+        <v>45175.7</v>
+      </c>
+      <c r="E634" t="n">
+        <v>45518.07</v>
+      </c>
+      <c r="F634" t="n">
+        <v>397.35</v>
+      </c>
+      <c r="G634" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H634" s="55">
+        <f>E634-G634</f>
+        <v/>
+      </c>
+      <c r="I634" s="34">
+        <f>H634/1000</f>
+        <v/>
+      </c>
+      <c r="J634" s="34">
+        <f>AVERAGE(I633:I634)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>45529.48</v>
+        <v>46216.41</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45518.07</v>
+        <v>46021.48</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N634"/>
+  <dimension ref="A1:N635"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26699,22 +26699,22 @@
       <c r="A634" s="62" t="n">
         <v>46246</v>
       </c>
-      <c r="B634" t="n">
+      <c r="B634" s="0" t="n">
         <v>45175.7</v>
       </c>
-      <c r="C634" t="n">
+      <c r="C634" s="0" t="n">
         <v>45529.48</v>
       </c>
-      <c r="D634" t="n">
+      <c r="D634" s="0" t="n">
         <v>45175.7</v>
       </c>
-      <c r="E634" t="n">
+      <c r="E634" s="0" t="n">
         <v>45518.07</v>
       </c>
-      <c r="F634" t="n">
+      <c r="F634" s="0" t="n">
         <v>397.35</v>
       </c>
-      <c r="G634" t="n">
+      <c r="G634" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H634" s="55">
@@ -26727,6 +26727,41 @@
       </c>
       <c r="J634" s="34">
         <f>AVERAGE(I633:I634)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="62" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B635" t="n">
+        <v>45676.54</v>
+      </c>
+      <c r="C635" t="n">
+        <v>46216.41</v>
+      </c>
+      <c r="D635" t="n">
+        <v>45676.54</v>
+      </c>
+      <c r="E635" t="n">
+        <v>46021.48</v>
+      </c>
+      <c r="F635" t="n">
+        <v>503.41</v>
+      </c>
+      <c r="G635" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H635" s="55">
+        <f>E635-G635</f>
+        <v/>
+      </c>
+      <c r="I635" s="34">
+        <f>H635/1000</f>
+        <v/>
+      </c>
+      <c r="J635" s="34">
+        <f>AVERAGE(I634:I635)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>46216.41</v>
+        <v>46402.6</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>46021.48</v>
+        <v>45811.01</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N635"/>
+  <dimension ref="A1:N636"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26734,22 +26734,22 @@
       <c r="A635" s="62" t="n">
         <v>46247</v>
       </c>
-      <c r="B635" t="n">
+      <c r="B635" s="0" t="n">
         <v>45676.54</v>
       </c>
-      <c r="C635" t="n">
+      <c r="C635" s="0" t="n">
         <v>46216.41</v>
       </c>
-      <c r="D635" t="n">
+      <c r="D635" s="0" t="n">
         <v>45676.54</v>
       </c>
-      <c r="E635" t="n">
+      <c r="E635" s="0" t="n">
         <v>46021.48</v>
       </c>
-      <c r="F635" t="n">
+      <c r="F635" s="0" t="n">
         <v>503.41</v>
       </c>
-      <c r="G635" t="n">
+      <c r="G635" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H635" s="55">
@@ -26762,6 +26762,41 @@
       </c>
       <c r="J635" s="34">
         <f>AVERAGE(I634:I635)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="62" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B636" t="n">
+        <v>46103.81</v>
+      </c>
+      <c r="C636" t="n">
+        <v>46402.6</v>
+      </c>
+      <c r="D636" t="n">
+        <v>45798.31</v>
+      </c>
+      <c r="E636" t="n">
+        <v>45811.01</v>
+      </c>
+      <c r="F636" t="n">
+        <v>-210.47</v>
+      </c>
+      <c r="G636" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H636" s="55">
+        <f>E636-G636</f>
+        <v/>
+      </c>
+      <c r="I636" s="34">
+        <f>H636/1000</f>
+        <v/>
+      </c>
+      <c r="J636" s="34">
+        <f>AVERAGE(I635:I636)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45811.01</v>
+        <v>45857.27</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N636"/>
+  <dimension ref="A1:N637"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26769,22 +26769,22 @@
       <c r="A636" s="62" t="n">
         <v>46248</v>
       </c>
-      <c r="B636" t="n">
+      <c r="B636" s="0" t="n">
         <v>46103.81</v>
       </c>
-      <c r="C636" t="n">
+      <c r="C636" s="0" t="n">
         <v>46402.6</v>
       </c>
-      <c r="D636" t="n">
+      <c r="D636" s="0" t="n">
         <v>45798.31</v>
       </c>
-      <c r="E636" t="n">
+      <c r="E636" s="0" t="n">
         <v>45811.01</v>
       </c>
-      <c r="F636" t="n">
+      <c r="F636" s="0" t="n">
         <v>-210.47</v>
       </c>
-      <c r="G636" t="n">
+      <c r="G636" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H636" s="55">
@@ -26797,6 +26797,41 @@
       </c>
       <c r="J636" s="34">
         <f>AVERAGE(I635:I636)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="62" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B637" t="n">
+        <v>45841.17</v>
+      </c>
+      <c r="C637" t="n">
+        <v>46189.3</v>
+      </c>
+      <c r="D637" t="n">
+        <v>45765.07</v>
+      </c>
+      <c r="E637" t="n">
+        <v>45857.27</v>
+      </c>
+      <c r="F637" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="G637" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H637" s="55">
+        <f>E637-G637</f>
+        <v/>
+      </c>
+      <c r="I637" s="34">
+        <f>H637/1000</f>
+        <v/>
+      </c>
+      <c r="J637" s="34">
+        <f>AVERAGE(I636:I637)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45857.27</v>
+        <v>45308.68</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N637"/>
+  <dimension ref="A1:N638"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26804,22 +26804,22 @@
       <c r="A637" s="62" t="n">
         <v>46251</v>
       </c>
-      <c r="B637" t="n">
+      <c r="B637" s="0" t="n">
         <v>45841.17</v>
       </c>
-      <c r="C637" t="n">
+      <c r="C637" s="0" t="n">
         <v>46189.3</v>
       </c>
-      <c r="D637" t="n">
+      <c r="D637" s="0" t="n">
         <v>45765.07</v>
       </c>
-      <c r="E637" t="n">
+      <c r="E637" s="0" t="n">
         <v>45857.27</v>
       </c>
-      <c r="F637" t="n">
+      <c r="F637" s="0" t="n">
         <v>46.26</v>
       </c>
-      <c r="G637" t="n">
+      <c r="G637" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H637" s="55">
@@ -26832,6 +26832,41 @@
       </c>
       <c r="J637" s="34">
         <f>AVERAGE(I636:I637)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="62" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B638" t="n">
+        <v>45922.4</v>
+      </c>
+      <c r="C638" t="n">
+        <v>46064.09</v>
+      </c>
+      <c r="D638" t="n">
+        <v>45225.42</v>
+      </c>
+      <c r="E638" t="n">
+        <v>45308.68</v>
+      </c>
+      <c r="F638" t="n">
+        <v>-548.59</v>
+      </c>
+      <c r="G638" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H638" s="55">
+        <f>E638-G638</f>
+        <v/>
+      </c>
+      <c r="I638" s="34">
+        <f>H638/1000</f>
+        <v/>
+      </c>
+      <c r="J638" s="34">
+        <f>AVERAGE(I637:I638)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45308.68</v>
+        <v>44719.35</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N638"/>
+  <dimension ref="A1:N639"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26839,22 +26839,22 @@
       <c r="A638" s="62" t="n">
         <v>46252</v>
       </c>
-      <c r="B638" t="n">
+      <c r="B638" s="0" t="n">
         <v>45922.4</v>
       </c>
-      <c r="C638" t="n">
+      <c r="C638" s="0" t="n">
         <v>46064.09</v>
       </c>
-      <c r="D638" t="n">
+      <c r="D638" s="0" t="n">
         <v>45225.42</v>
       </c>
-      <c r="E638" t="n">
+      <c r="E638" s="0" t="n">
         <v>45308.68</v>
       </c>
-      <c r="F638" t="n">
+      <c r="F638" s="0" t="n">
         <v>-548.59</v>
       </c>
-      <c r="G638" t="n">
+      <c r="G638" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H638" s="55">
@@ -26867,6 +26867,41 @@
       </c>
       <c r="J638" s="34">
         <f>AVERAGE(I637:I638)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="62" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B639" t="n">
+        <v>45071.34</v>
+      </c>
+      <c r="C639" t="n">
+        <v>45071.34</v>
+      </c>
+      <c r="D639" t="n">
+        <v>44308.71</v>
+      </c>
+      <c r="E639" t="n">
+        <v>44719.35</v>
+      </c>
+      <c r="F639" t="n">
+        <v>-589.33</v>
+      </c>
+      <c r="G639" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H639" s="55">
+        <f>E639-G639</f>
+        <v/>
+      </c>
+      <c r="I639" s="34">
+        <f>H639/1000</f>
+        <v/>
+      </c>
+      <c r="J639" s="34">
+        <f>AVERAGE(I638:I639)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -26874,22 +26873,22 @@
       <c r="A639" s="62" t="n">
         <v>46253</v>
       </c>
-      <c r="B639" t="n">
+      <c r="B639" s="0" t="n">
         <v>45071.34</v>
       </c>
-      <c r="C639" t="n">
+      <c r="C639" s="0" t="n">
         <v>45071.34</v>
       </c>
-      <c r="D639" t="n">
+      <c r="D639" s="0" t="n">
         <v>44308.71</v>
       </c>
-      <c r="E639" t="n">
+      <c r="E639" s="0" t="n">
         <v>44719.35</v>
       </c>
-      <c r="F639" t="n">
+      <c r="F639" s="0" t="n">
         <v>-589.33</v>
       </c>
-      <c r="G639" t="n">
+      <c r="G639" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H639" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3112,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3124,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44719.35</v>
+        <v>45224.29</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3156,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N639"/>
+  <dimension ref="A1:N641"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26904,6 +26905,76 @@
         <v/>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="62" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B640" t="n">
+        <v>44942.01</v>
+      </c>
+      <c r="C640" t="n">
+        <v>45160.05</v>
+      </c>
+      <c r="D640" t="n">
+        <v>44446.36</v>
+      </c>
+      <c r="E640" t="n">
+        <v>44933.74</v>
+      </c>
+      <c r="F640" t="n">
+        <v>214.39</v>
+      </c>
+      <c r="G640" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H640" s="55">
+        <f>E640-G640</f>
+        <v/>
+      </c>
+      <c r="I640" s="34">
+        <f>H640/1000</f>
+        <v/>
+      </c>
+      <c r="J640" s="34">
+        <f>AVERAGE(I639:I640)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="62" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B641" t="n">
+        <v>44923.34</v>
+      </c>
+      <c r="C641" t="n">
+        <v>45254.84</v>
+      </c>
+      <c r="D641" t="n">
+        <v>44583.87</v>
+      </c>
+      <c r="E641" t="n">
+        <v>45224.29</v>
+      </c>
+      <c r="F641" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="G641" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H641" s="55">
+        <f>E641-G641</f>
+        <v/>
+      </c>
+      <c r="I641" s="34">
+        <f>H641/1000</f>
+        <v/>
+      </c>
+      <c r="J641" s="34">
+        <f>AVERAGE(I640:I641)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45224.29</v>
+        <v>44762.32</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N641"/>
+  <dimension ref="A1:N642"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26909,22 +26909,22 @@
       <c r="A640" s="62" t="n">
         <v>46254</v>
       </c>
-      <c r="B640" t="n">
+      <c r="B640" s="0" t="n">
         <v>44942.01</v>
       </c>
-      <c r="C640" t="n">
+      <c r="C640" s="0" t="n">
         <v>45160.05</v>
       </c>
-      <c r="D640" t="n">
+      <c r="D640" s="0" t="n">
         <v>44446.36</v>
       </c>
-      <c r="E640" t="n">
+      <c r="E640" s="0" t="n">
         <v>44933.74</v>
       </c>
-      <c r="F640" t="n">
+      <c r="F640" s="0" t="n">
         <v>214.39</v>
       </c>
-      <c r="G640" t="n">
+      <c r="G640" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H640" s="55">
@@ -26944,22 +26944,22 @@
       <c r="A641" s="62" t="n">
         <v>46255</v>
       </c>
-      <c r="B641" t="n">
+      <c r="B641" s="0" t="n">
         <v>44923.34</v>
       </c>
-      <c r="C641" t="n">
+      <c r="C641" s="0" t="n">
         <v>45254.84</v>
       </c>
-      <c r="D641" t="n">
+      <c r="D641" s="0" t="n">
         <v>44583.87</v>
       </c>
-      <c r="E641" t="n">
+      <c r="E641" s="0" t="n">
         <v>45224.29</v>
       </c>
-      <c r="F641" t="n">
+      <c r="F641" s="0" t="n">
         <v>290.55</v>
       </c>
-      <c r="G641" t="n">
+      <c r="G641" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H641" s="55">
@@ -26972,6 +26972,41 @@
       </c>
       <c r="J641" s="34">
         <f>AVERAGE(I640:I641)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="62" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B642" t="n">
+        <v>45240.3</v>
+      </c>
+      <c r="C642" t="n">
+        <v>45362.3</v>
+      </c>
+      <c r="D642" t="n">
+        <v>44761.88</v>
+      </c>
+      <c r="E642" t="n">
+        <v>44762.32</v>
+      </c>
+      <c r="F642" t="n">
+        <v>-461.97</v>
+      </c>
+      <c r="G642" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H642" s="55">
+        <f>E642-G642</f>
+        <v/>
+      </c>
+      <c r="I642" s="34">
+        <f>H642/1000</f>
+        <v/>
+      </c>
+      <c r="J642" s="34">
+        <f>AVERAGE(I641:I642)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>44762.32</v>
+        <v>45169.46</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N642"/>
+  <dimension ref="A1:N643"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -26979,22 +26979,22 @@
       <c r="A642" s="62" t="n">
         <v>46258</v>
       </c>
-      <c r="B642" t="n">
+      <c r="B642" s="0" t="n">
         <v>45240.3</v>
       </c>
-      <c r="C642" t="n">
+      <c r="C642" s="0" t="n">
         <v>45362.3</v>
       </c>
-      <c r="D642" t="n">
+      <c r="D642" s="0" t="n">
         <v>44761.88</v>
       </c>
-      <c r="E642" t="n">
+      <c r="E642" s="0" t="n">
         <v>44762.32</v>
       </c>
-      <c r="F642" t="n">
+      <c r="F642" s="0" t="n">
         <v>-461.97</v>
       </c>
-      <c r="G642" t="n">
+      <c r="G642" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H642" s="55">
@@ -27007,6 +27007,41 @@
       </c>
       <c r="J642" s="34">
         <f>AVERAGE(I641:I642)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="62" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B643" t="n">
+        <v>44728.36</v>
+      </c>
+      <c r="C643" t="n">
+        <v>45169.46</v>
+      </c>
+      <c r="D643" t="n">
+        <v>44210.31</v>
+      </c>
+      <c r="E643" t="n">
+        <v>45169.46</v>
+      </c>
+      <c r="F643" t="n">
+        <v>407.14</v>
+      </c>
+      <c r="G643" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H643" s="55">
+        <f>E643-G643</f>
+        <v/>
+      </c>
+      <c r="I643" s="34">
+        <f>H643/1000</f>
+        <v/>
+      </c>
+      <c r="J643" s="34">
+        <f>AVERAGE(I642:I643)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45169.46</v>
+        <v>45832.62</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N643"/>
+  <dimension ref="A1:N644"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27014,22 +27014,22 @@
       <c r="A643" s="62" t="n">
         <v>46259</v>
       </c>
-      <c r="B643" t="n">
+      <c r="B643" s="0" t="n">
         <v>44728.36</v>
       </c>
-      <c r="C643" t="n">
+      <c r="C643" s="0" t="n">
         <v>45169.46</v>
       </c>
-      <c r="D643" t="n">
+      <c r="D643" s="0" t="n">
         <v>44210.31</v>
       </c>
-      <c r="E643" t="n">
+      <c r="E643" s="0" t="n">
         <v>45169.46</v>
       </c>
-      <c r="F643" t="n">
+      <c r="F643" s="0" t="n">
         <v>407.14</v>
       </c>
-      <c r="G643" t="n">
+      <c r="G643" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H643" s="55">
@@ -27042,6 +27042,41 @@
       </c>
       <c r="J643" s="34">
         <f>AVERAGE(I642:I643)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="62" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B644" t="n">
+        <v>45157.64</v>
+      </c>
+      <c r="C644" t="n">
+        <v>45878.39</v>
+      </c>
+      <c r="D644" t="n">
+        <v>44925.84</v>
+      </c>
+      <c r="E644" t="n">
+        <v>45832.62</v>
+      </c>
+      <c r="F644" t="n">
+        <v>663.16</v>
+      </c>
+      <c r="G644" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H644" s="55">
+        <f>E644-G644</f>
+        <v/>
+      </c>
+      <c r="I644" s="34">
+        <f>H644/1000</f>
+        <v/>
+      </c>
+      <c r="J644" s="34">
+        <f>AVERAGE(I643:I644)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>46402.6</v>
+        <v>46574.52</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>45832.62</v>
+        <v>46331.45</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N644"/>
+  <dimension ref="A1:N646"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27049,22 +27049,22 @@
       <c r="A644" s="62" t="n">
         <v>46260</v>
       </c>
-      <c r="B644" t="n">
+      <c r="B644" s="0" t="n">
         <v>45157.64</v>
       </c>
-      <c r="C644" t="n">
+      <c r="C644" s="0" t="n">
         <v>45878.39</v>
       </c>
-      <c r="D644" t="n">
+      <c r="D644" s="0" t="n">
         <v>44925.84</v>
       </c>
-      <c r="E644" t="n">
+      <c r="E644" s="0" t="n">
         <v>45832.62</v>
       </c>
-      <c r="F644" t="n">
+      <c r="F644" s="0" t="n">
         <v>663.16</v>
       </c>
-      <c r="G644" t="n">
+      <c r="G644" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H644" s="55">
@@ -27077,6 +27077,76 @@
       </c>
       <c r="J644" s="34">
         <f>AVERAGE(I643:I644)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="62" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B645" t="n">
+        <v>45890.18</v>
+      </c>
+      <c r="C645" t="n">
+        <v>46401.78</v>
+      </c>
+      <c r="D645" t="n">
+        <v>45890.18</v>
+      </c>
+      <c r="E645" t="n">
+        <v>45975.22</v>
+      </c>
+      <c r="F645" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="G645" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H645" s="55">
+        <f>E645-G645</f>
+        <v/>
+      </c>
+      <c r="I645" s="34">
+        <f>H645/1000</f>
+        <v/>
+      </c>
+      <c r="J645" s="34">
+        <f>AVERAGE(I644:I645)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="62" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B646" t="n">
+        <v>46070.83</v>
+      </c>
+      <c r="C646" t="n">
+        <v>46574.52</v>
+      </c>
+      <c r="D646" t="n">
+        <v>46070.83</v>
+      </c>
+      <c r="E646" t="n">
+        <v>46331.45</v>
+      </c>
+      <c r="F646" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="G646" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H646" s="55">
+        <f>E646-G646</f>
+        <v/>
+      </c>
+      <c r="I646" s="34">
+        <f>H646/1000</f>
+        <v/>
+      </c>
+      <c r="J646" s="34">
+        <f>AVERAGE(I645:I646)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B53" s="0" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>42780.42</v>
@@ -3125,7 +3125,7 @@
         <v>42780.42</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>46331.45</v>
+        <v>46128.47</v>
       </c>
       <c r="G53" s="0" t="n">
         <v>47395.3</v>
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N646"/>
+  <dimension ref="A1:N647"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27084,22 +27084,22 @@
       <c r="A645" s="62" t="n">
         <v>46261</v>
       </c>
-      <c r="B645" t="n">
+      <c r="B645" s="0" t="n">
         <v>45890.18</v>
       </c>
-      <c r="C645" t="n">
+      <c r="C645" s="0" t="n">
         <v>46401.78</v>
       </c>
-      <c r="D645" t="n">
+      <c r="D645" s="0" t="n">
         <v>45890.18</v>
       </c>
-      <c r="E645" t="n">
+      <c r="E645" s="0" t="n">
         <v>45975.22</v>
       </c>
-      <c r="F645" t="n">
+      <c r="F645" s="0" t="n">
         <v>142.6</v>
       </c>
-      <c r="G645" t="n">
+      <c r="G645" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H645" s="55">
@@ -27119,22 +27119,22 @@
       <c r="A646" s="62" t="n">
         <v>46262</v>
       </c>
-      <c r="B646" t="n">
+      <c r="B646" s="0" t="n">
         <v>46070.83</v>
       </c>
-      <c r="C646" t="n">
+      <c r="C646" s="0" t="n">
         <v>46574.52</v>
       </c>
-      <c r="D646" t="n">
+      <c r="D646" s="0" t="n">
         <v>46070.83</v>
       </c>
-      <c r="E646" t="n">
+      <c r="E646" s="0" t="n">
         <v>46331.45</v>
       </c>
-      <c r="F646" t="n">
+      <c r="F646" s="0" t="n">
         <v>356.23</v>
       </c>
-      <c r="G646" t="n">
+      <c r="G646" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H646" s="55">
@@ -27147,6 +27147,41 @@
       </c>
       <c r="J646" s="34">
         <f>AVERAGE(I645:I646)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="62" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B647" t="n">
+        <v>46224.69</v>
+      </c>
+      <c r="C647" t="n">
+        <v>46224.69</v>
+      </c>
+      <c r="D647" t="n">
+        <v>45450.21</v>
+      </c>
+      <c r="E647" t="n">
+        <v>46128.47</v>
+      </c>
+      <c r="F647" t="n">
+        <v>-202.98</v>
+      </c>
+      <c r="G647" t="n">
+        <v>43801.86</v>
+      </c>
+      <c r="H647" s="55">
+        <f>E647-G647</f>
+        <v/>
+      </c>
+      <c r="I647" s="34">
+        <f>H647/1000</f>
+        <v/>
+      </c>
+      <c r="J647" s="34">
+        <f>AVERAGE(I646:I647)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="6.5" defaultRowHeight="16.5"/>
   <cols>
     <col width="5.875" customWidth="1" style="1" min="1" max="1"/>
@@ -3141,8 +3141,42 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>26M09</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>46177.11</v>
+      </c>
+      <c r="D54" t="n">
+        <v>46948.72</v>
+      </c>
+      <c r="E54" t="n">
+        <v>46081.11</v>
+      </c>
+      <c r="F54" t="n">
+        <v>46948.72</v>
+      </c>
+      <c r="G54" t="n">
+        <v>46948.72</v>
+      </c>
+      <c r="H54" t="n">
+        <v>42780.42</v>
+      </c>
+      <c r="I54" t="n">
+        <v>44864.57</v>
+      </c>
       <c r="J54" s="0" t="n">
         <v>43390.075</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="J55" t="n">
+        <v>44864.57</v>
       </c>
     </row>
   </sheetData>
@@ -3157,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N647"/>
+  <dimension ref="A1:N648"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27154,22 +27188,22 @@
       <c r="A647" s="62" t="n">
         <v>46265</v>
       </c>
-      <c r="B647" t="n">
+      <c r="B647" s="0" t="n">
         <v>46224.69</v>
       </c>
-      <c r="C647" t="n">
+      <c r="C647" s="0" t="n">
         <v>46224.69</v>
       </c>
-      <c r="D647" t="n">
+      <c r="D647" s="0" t="n">
         <v>45450.21</v>
       </c>
-      <c r="E647" t="n">
+      <c r="E647" s="0" t="n">
         <v>46128.47</v>
       </c>
-      <c r="F647" t="n">
+      <c r="F647" s="0" t="n">
         <v>-202.98</v>
       </c>
-      <c r="G647" t="n">
+      <c r="G647" s="0" t="n">
         <v>43801.86</v>
       </c>
       <c r="H647" s="55">
@@ -27182,6 +27216,41 @@
       </c>
       <c r="J647" s="34">
         <f>AVERAGE(I646:I647)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="62" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B648" t="n">
+        <v>46177.11</v>
+      </c>
+      <c r="C648" t="n">
+        <v>46948.72</v>
+      </c>
+      <c r="D648" t="n">
+        <v>46081.11</v>
+      </c>
+      <c r="E648" t="n">
+        <v>46948.72</v>
+      </c>
+      <c r="F648" t="n">
+        <v>820.25</v>
+      </c>
+      <c r="G648" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H648" s="55">
+        <f>E648-G648</f>
+        <v/>
+      </c>
+      <c r="I648" s="34">
+        <f>H648/1000</f>
+        <v/>
+      </c>
+      <c r="J648" s="34">
+        <f>AVERAGE(I647:I648)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3141,33 +3141,33 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>26M09</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="0" t="n">
         <v>46177.11</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>46948.72</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>46081.11</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="0" t="n">
+        <v>46164.72</v>
+      </c>
+      <c r="G54" s="0" t="n">
         <v>46948.72</v>
       </c>
-      <c r="G54" t="n">
-        <v>46948.72</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="H54" s="0" t="n">
         <v>42780.42</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="0" t="n">
         <v>44864.57</v>
       </c>
       <c r="J54" s="0" t="n">
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="J55" t="n">
+      <c r="J55" s="0" t="n">
         <v>44864.57</v>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N648"/>
+  <dimension ref="A1:N649"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27223,22 +27223,22 @@
       <c r="A648" s="62" t="n">
         <v>46266</v>
       </c>
-      <c r="B648" t="n">
+      <c r="B648" s="0" t="n">
         <v>46177.11</v>
       </c>
-      <c r="C648" t="n">
+      <c r="C648" s="0" t="n">
         <v>46948.72</v>
       </c>
-      <c r="D648" t="n">
+      <c r="D648" s="0" t="n">
         <v>46081.11</v>
       </c>
-      <c r="E648" t="n">
+      <c r="E648" s="0" t="n">
         <v>46948.72</v>
       </c>
-      <c r="F648" t="n">
+      <c r="F648" s="0" t="n">
         <v>820.25</v>
       </c>
-      <c r="G648" t="n">
+      <c r="G648" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H648" s="55">
@@ -27251,6 +27251,41 @@
       </c>
       <c r="J648" s="34">
         <f>AVERAGE(I647:I648)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="62" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B649" t="n">
+        <v>46901.32</v>
+      </c>
+      <c r="C649" t="n">
+        <v>46946.6</v>
+      </c>
+      <c r="D649" t="n">
+        <v>46164.72</v>
+      </c>
+      <c r="E649" t="n">
+        <v>46164.72</v>
+      </c>
+      <c r="F649" t="n">
+        <v>-784</v>
+      </c>
+      <c r="G649" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H649" s="55">
+        <f>E649-G649</f>
+        <v/>
+      </c>
+      <c r="I649" s="34">
+        <f>H649/1000</f>
+        <v/>
+      </c>
+      <c r="J649" s="34">
+        <f>AVERAGE(I648:I649)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3156,10 +3156,10 @@
         <v>46948.72</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>46081.11</v>
+        <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>46164.72</v>
+        <v>45857.66</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>46948.72</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N649"/>
+  <dimension ref="A1:N650"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27258,22 +27258,22 @@
       <c r="A649" s="62" t="n">
         <v>46267</v>
       </c>
-      <c r="B649" t="n">
+      <c r="B649" s="0" t="n">
         <v>46901.32</v>
       </c>
-      <c r="C649" t="n">
+      <c r="C649" s="0" t="n">
         <v>46946.6</v>
       </c>
-      <c r="D649" t="n">
+      <c r="D649" s="0" t="n">
         <v>46164.72</v>
       </c>
-      <c r="E649" t="n">
+      <c r="E649" s="0" t="n">
         <v>46164.72</v>
       </c>
-      <c r="F649" t="n">
+      <c r="F649" s="0" t="n">
         <v>-784</v>
       </c>
-      <c r="G649" t="n">
+      <c r="G649" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H649" s="55">
@@ -27286,6 +27286,41 @@
       </c>
       <c r="J649" s="34">
         <f>AVERAGE(I648:I649)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="62" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B650" t="n">
+        <v>46325.48</v>
+      </c>
+      <c r="C650" t="n">
+        <v>46517.45</v>
+      </c>
+      <c r="D650" t="n">
+        <v>45839.36</v>
+      </c>
+      <c r="E650" t="n">
+        <v>45857.66</v>
+      </c>
+      <c r="F650" t="n">
+        <v>-307.06</v>
+      </c>
+      <c r="G650" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H650" s="55">
+        <f>E650-G650</f>
+        <v/>
+      </c>
+      <c r="I650" s="34">
+        <f>H650/1000</f>
+        <v/>
+      </c>
+      <c r="J650" s="34">
+        <f>AVERAGE(I649:I650)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>45857.66</v>
+        <v>46551.13</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>46948.72</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N650"/>
+  <dimension ref="A1:N651"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27293,22 +27293,22 @@
       <c r="A650" s="62" t="n">
         <v>46268</v>
       </c>
-      <c r="B650" t="n">
+      <c r="B650" s="0" t="n">
         <v>46325.48</v>
       </c>
-      <c r="C650" t="n">
+      <c r="C650" s="0" t="n">
         <v>46517.45</v>
       </c>
-      <c r="D650" t="n">
+      <c r="D650" s="0" t="n">
         <v>45839.36</v>
       </c>
-      <c r="E650" t="n">
+      <c r="E650" s="0" t="n">
         <v>45857.66</v>
       </c>
-      <c r="F650" t="n">
+      <c r="F650" s="0" t="n">
         <v>-307.06</v>
       </c>
-      <c r="G650" t="n">
+      <c r="G650" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H650" s="55">
@@ -27321,6 +27321,41 @@
       </c>
       <c r="J650" s="34">
         <f>AVERAGE(I649:I650)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="62" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B651" t="n">
+        <v>45991.28</v>
+      </c>
+      <c r="C651" t="n">
+        <v>46620.96</v>
+      </c>
+      <c r="D651" t="n">
+        <v>45966.86</v>
+      </c>
+      <c r="E651" t="n">
+        <v>46551.13</v>
+      </c>
+      <c r="F651" t="n">
+        <v>693.47</v>
+      </c>
+      <c r="G651" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H651" s="55">
+        <f>E651-G651</f>
+        <v/>
+      </c>
+      <c r="I651" s="34">
+        <f>H651/1000</f>
+        <v/>
+      </c>
+      <c r="J651" s="34">
+        <f>AVERAGE(I650:I651)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>46948.72</v>
+        <v>47429.58</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>46551.13</v>
+        <v>47326.27</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>46948.72</v>
+        <v>47429.58</v>
       </c>
       <c r="H54" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>44864.57</v>
+        <v>45105</v>
       </c>
       <c r="J54" s="0" t="n">
         <v>43390.075</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="55">
       <c r="J55" s="0" t="n">
-        <v>44864.57</v>
+        <v>45105</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N651"/>
+  <dimension ref="A1:N652"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27328,22 +27328,22 @@
       <c r="A651" s="62" t="n">
         <v>46269</v>
       </c>
-      <c r="B651" t="n">
+      <c r="B651" s="0" t="n">
         <v>45991.28</v>
       </c>
-      <c r="C651" t="n">
+      <c r="C651" s="0" t="n">
         <v>46620.96</v>
       </c>
-      <c r="D651" t="n">
+      <c r="D651" s="0" t="n">
         <v>45966.86</v>
       </c>
-      <c r="E651" t="n">
+      <c r="E651" s="0" t="n">
         <v>46551.13</v>
       </c>
-      <c r="F651" t="n">
+      <c r="F651" s="0" t="n">
         <v>693.47</v>
       </c>
-      <c r="G651" t="n">
+      <c r="G651" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H651" s="55">
@@ -27356,6 +27356,41 @@
       </c>
       <c r="J651" s="34">
         <f>AVERAGE(I650:I651)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="62" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B652" t="n">
+        <v>46724</v>
+      </c>
+      <c r="C652" t="n">
+        <v>47429.58</v>
+      </c>
+      <c r="D652" t="n">
+        <v>46724</v>
+      </c>
+      <c r="E652" t="n">
+        <v>47326.27</v>
+      </c>
+      <c r="F652" t="n">
+        <v>775.14</v>
+      </c>
+      <c r="G652" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H652" s="55">
+        <f>E652-G652</f>
+        <v/>
+      </c>
+      <c r="I652" s="34">
+        <f>H652/1000</f>
+        <v/>
+      </c>
+      <c r="J652" s="34">
+        <f>AVERAGE(I651:I652)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>47429.58</v>
+        <v>47578.24</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47326.27</v>
+        <v>47105.78</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>47429.58</v>
+        <v>47578.24</v>
       </c>
       <c r="H54" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>45105</v>
+        <v>45179.33</v>
       </c>
       <c r="J54" s="0" t="n">
         <v>43390.075</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="55">
       <c r="J55" s="0" t="n">
-        <v>45105</v>
+        <v>45179.33</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N652"/>
+  <dimension ref="A1:N653"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27363,22 +27363,22 @@
       <c r="A652" s="62" t="n">
         <v>46272</v>
       </c>
-      <c r="B652" t="n">
+      <c r="B652" s="0" t="n">
         <v>46724</v>
       </c>
-      <c r="C652" t="n">
+      <c r="C652" s="0" t="n">
         <v>47429.58</v>
       </c>
-      <c r="D652" t="n">
+      <c r="D652" s="0" t="n">
         <v>46724</v>
       </c>
-      <c r="E652" t="n">
+      <c r="E652" s="0" t="n">
         <v>47326.27</v>
       </c>
-      <c r="F652" t="n">
+      <c r="F652" s="0" t="n">
         <v>775.14</v>
       </c>
-      <c r="G652" t="n">
+      <c r="G652" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H652" s="55">
@@ -27391,6 +27391,41 @@
       </c>
       <c r="J652" s="34">
         <f>AVERAGE(I651:I652)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="62" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B653" t="n">
+        <v>47335.24</v>
+      </c>
+      <c r="C653" t="n">
+        <v>47578.24</v>
+      </c>
+      <c r="D653" t="n">
+        <v>47023.73</v>
+      </c>
+      <c r="E653" t="n">
+        <v>47105.78</v>
+      </c>
+      <c r="F653" t="n">
+        <v>-220.49</v>
+      </c>
+      <c r="G653" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H653" s="55">
+        <f>E653-G653</f>
+        <v/>
+      </c>
+      <c r="I653" s="34">
+        <f>H653/1000</f>
+        <v/>
+      </c>
+      <c r="J653" s="34">
+        <f>AVERAGE(I652:I653)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47105.78</v>
+        <v>47183.36</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N653"/>
+  <dimension ref="A1:N654"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27398,22 +27398,22 @@
       <c r="A653" s="62" t="n">
         <v>46273</v>
       </c>
-      <c r="B653" t="n">
+      <c r="B653" s="0" t="n">
         <v>47335.24</v>
       </c>
-      <c r="C653" t="n">
+      <c r="C653" s="0" t="n">
         <v>47578.24</v>
       </c>
-      <c r="D653" t="n">
+      <c r="D653" s="0" t="n">
         <v>47023.73</v>
       </c>
-      <c r="E653" t="n">
+      <c r="E653" s="0" t="n">
         <v>47105.78</v>
       </c>
-      <c r="F653" t="n">
+      <c r="F653" s="0" t="n">
         <v>-220.49</v>
       </c>
-      <c r="G653" t="n">
+      <c r="G653" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H653" s="55">
@@ -27426,6 +27426,41 @@
       </c>
       <c r="J653" s="34">
         <f>AVERAGE(I652:I653)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="62" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B654" t="n">
+        <v>47142.74</v>
+      </c>
+      <c r="C654" t="n">
+        <v>47548.26</v>
+      </c>
+      <c r="D654" t="n">
+        <v>47060.78</v>
+      </c>
+      <c r="E654" t="n">
+        <v>47183.36</v>
+      </c>
+      <c r="F654" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="G654" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H654" s="55">
+        <f>E654-G654</f>
+        <v/>
+      </c>
+      <c r="I654" s="34">
+        <f>H654/1000</f>
+        <v/>
+      </c>
+      <c r="J654" s="34">
+        <f>AVERAGE(I653:I654)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47183.36</v>
+        <v>46940.49</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N654"/>
+  <dimension ref="A1:N655"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27433,22 +27433,22 @@
       <c r="A654" s="62" t="n">
         <v>46274</v>
       </c>
-      <c r="B654" t="n">
+      <c r="B654" s="0" t="n">
         <v>47142.74</v>
       </c>
-      <c r="C654" t="n">
+      <c r="C654" s="0" t="n">
         <v>47548.26</v>
       </c>
-      <c r="D654" t="n">
+      <c r="D654" s="0" t="n">
         <v>47060.78</v>
       </c>
-      <c r="E654" t="n">
+      <c r="E654" s="0" t="n">
         <v>47183.36</v>
       </c>
-      <c r="F654" t="n">
+      <c r="F654" s="0" t="n">
         <v>77.58</v>
       </c>
-      <c r="G654" t="n">
+      <c r="G654" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H654" s="55">
@@ -27461,6 +27461,41 @@
       </c>
       <c r="J654" s="34">
         <f>AVERAGE(I653:I654)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="62" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B655" t="n">
+        <v>47130.96</v>
+      </c>
+      <c r="C655" t="n">
+        <v>47130.96</v>
+      </c>
+      <c r="D655" t="n">
+        <v>46573.47</v>
+      </c>
+      <c r="E655" t="n">
+        <v>46940.49</v>
+      </c>
+      <c r="F655" t="n">
+        <v>-242.87</v>
+      </c>
+      <c r="G655" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H655" s="55">
+        <f>E655-G655</f>
+        <v/>
+      </c>
+      <c r="I655" s="34">
+        <f>H655/1000</f>
+        <v/>
+      </c>
+      <c r="J655" s="34">
+        <f>AVERAGE(I654:I655)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45839.36</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>46940.49</v>
+        <v>46184.85</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N655"/>
+  <dimension ref="A1:N656"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27468,22 +27468,22 @@
       <c r="A655" s="62" t="n">
         <v>46275</v>
       </c>
-      <c r="B655" t="n">
+      <c r="B655" s="0" t="n">
         <v>47130.96</v>
       </c>
-      <c r="C655" t="n">
+      <c r="C655" s="0" t="n">
         <v>47130.96</v>
       </c>
-      <c r="D655" t="n">
+      <c r="D655" s="0" t="n">
         <v>46573.47</v>
       </c>
-      <c r="E655" t="n">
+      <c r="E655" s="0" t="n">
         <v>46940.49</v>
       </c>
-      <c r="F655" t="n">
+      <c r="F655" s="0" t="n">
         <v>-242.87</v>
       </c>
-      <c r="G655" t="n">
+      <c r="G655" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H655" s="55">
@@ -27496,6 +27496,41 @@
       </c>
       <c r="J655" s="34">
         <f>AVERAGE(I654:I655)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="62" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B656" t="n">
+        <v>46651.21</v>
+      </c>
+      <c r="C656" t="n">
+        <v>46651.21</v>
+      </c>
+      <c r="D656" t="n">
+        <v>45942.44</v>
+      </c>
+      <c r="E656" t="n">
+        <v>46184.85</v>
+      </c>
+      <c r="F656" t="n">
+        <v>-755.64</v>
+      </c>
+      <c r="G656" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H656" s="55">
+        <f>E656-G656</f>
+        <v/>
+      </c>
+      <c r="I656" s="34">
+        <f>H656/1000</f>
+        <v/>
+      </c>
+      <c r="J656" s="34">
+        <f>AVERAGE(I655:I656)</f>
         <v/>
       </c>
     </row>
